--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488200_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488200_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7443</v>
+        <v>2.2177</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9877</v>
+        <v>2.3229</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7566000000000001</v>
+        <v>-0.1052</v>
       </c>
       <c r="G2" t="n">
         <v>1.7593</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9855</v>
+        <v>1.459</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0606</v>
+        <v>0.3958</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9249</v>
+        <v>1.0632</v>
       </c>
       <c r="V2" t="n">
         <v>-0.63</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3415</v>
+        <v>1.8513</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9207</v>
+        <v>0.529</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4208</v>
+        <v>1.3223</v>
       </c>
       <c r="G3" t="n">
         <v>1.2618</v>
@@ -688,13 +688,13 @@
         <v>0.3706</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7091</v>
+        <v>0.2189</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4887</v>
+        <v>0.097</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2203</v>
+        <v>0.1219</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. FERNÁNDEZ HERNÁNDEZ</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6441</v>
+        <v>0.7265</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6441</v>
+        <v>2.5629</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.8364</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6441</v>
+        <v>1.8232</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6441</v>
+        <v>0.8693</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.9538</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6441</v>
+        <v>2.449</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6441</v>
+        <v>1.7949</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.6541</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.6258</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.9255</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.2997</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.041</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.3656</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.3245</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. PENAS REINO</t>
+          <t>J. FERNÁNDEZ HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,37 +799,37 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1302</v>
+        <v>0.6441</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0332</v>
+        <v>0.6441</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1634</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.152</v>
+        <v>0.6441</v>
       </c>
       <c r="H5" t="n">
-        <v>0.152</v>
+        <v>0.6441</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0215</v>
+        <v>0.6441</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0215</v>
+        <v>0.6441</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0219</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0547</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0328</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>D. PENAS REINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2292</v>
+        <v>0.1794</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7795</v>
+        <v>-0.0332</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0088</v>
+        <v>0.2126</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8232</v>
+        <v>0.152</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8693</v>
+        <v>0.152</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9538</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.449</v>
+        <v>0.0215</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7949</v>
+        <v>0.0215</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6541</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6258</v>
+        <v>0.1306</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9255</v>
+        <v>0.1306</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2997</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9968</v>
+        <v>0.0274</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.149</v>
+        <v>-0.0547</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1522</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.8321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4731</v>
+        <v>-1.0075</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4222</v>
+        <v>-0.0305</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0509</v>
+        <v>-0.977</v>
       </c>
       <c r="G7" t="n">
         <v>3.3203</v>
@@ -1000,13 +1000,13 @@
         <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2206</v>
+        <v>0.245</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7113</v>
+        <v>-0.3196</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4907</v>
+        <v>0.5645</v>
       </c>
       <c r="V7" t="n">
         <v>-3.461</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7904</v>
+        <v>-1.5453</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5791</v>
+        <v>-1.3833</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2113</v>
+        <v>-0.162</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0259</v>
@@ -1078,13 +1078,13 @@
         <v>1.1117</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5887</v>
+        <v>0.8338</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0037</v>
+        <v>0.1921</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5924</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0.3144</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FROUFE PEREZ</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9945</v>
+        <v>-2.0145</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.99</v>
+        <v>-1.4908</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9955</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.629</v>
+        <v>-0.5483</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2326</v>
+        <v>0.8786</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3965</v>
+        <v>-1.4269</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.0014</v>
+        <v>-0.6277</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.044</v>
+        <v>0.5536</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9573</v>
+        <v>-1.1813</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3723</v>
+        <v>0.0795</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1885</v>
+        <v>0.325</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5609</v>
+        <v>-0.2456</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1853</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4487</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8643</v>
+        <v>0.028</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5844</v>
+        <v>0.914</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6289</v>
+        <v>0.0005</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6289</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0872</v>
+        <v>-2.4615</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6866</v>
+        <v>-1.6444</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4006</v>
+        <v>-0.8171</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5483</v>
+        <v>-2.3341</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8786</v>
+        <v>-0.1973</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4269</v>
+        <v>-2.1368</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6277</v>
+        <v>-1.7225</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5536</v>
+        <v>0.2147</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1813</v>
+        <v>-1.9372</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0795</v>
+        <v>-0.6115</v>
       </c>
       <c r="N10" t="n">
-        <v>0.325</v>
+        <v>-0.412</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2456</v>
+        <v>-0.1996</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4087</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>-1.1117</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8692</v>
+        <v>0.2431</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1679</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0371</v>
+        <v>0.3121</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8883</v>
+        <v>1.2589</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8877</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>A. FROUFE PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2214</v>
+        <v>-2.7779</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.232</v>
+        <v>-4.7734</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9895</v>
+        <v>1.9955</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3341</v>
+        <v>-2.629</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1973</v>
+        <v>-1.2326</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1368</v>
+        <v>-1.3965</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7225</v>
+        <v>-3.0014</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2147</v>
+        <v>-1.044</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9372</v>
+        <v>-1.9573</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6115</v>
+        <v>0.3723</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.412</v>
+        <v>-0.1885</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1996</v>
+        <v>0.5609</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3706</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1117</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5168</v>
+        <v>0.6653</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6566</v>
+        <v>0.0809</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1398</v>
+        <v>0.5844</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4483</v>
+        <v>-5.1965</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3996</v>
+        <v>-3.7141</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0487</v>
+        <v>-1.4824</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6649</v>
@@ -1390,13 +1390,13 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1508</v>
+        <v>0.101</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.149</v>
+        <v>-0.4635</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0018</v>
+        <v>0.5645</v>
       </c>
       <c r="V12" t="n">
         <v>-0.0005</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.384</v>
+        <v>-9.3842</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.010700000000002</v>
+        <v>-7.0108</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3735</v>
+        <v>-2.3734</v>
       </c>
       <c r="G13" t="n">
         <v>1.7585</v>
@@ -1447,7 +1447,7 @@
         <v>12.752</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.027099999999999</v>
+        <v>-8.027100000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-2.9661</v>
@@ -1468,7 +1468,7 @@
         <v>9.264299999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>4.694300000000001</v>
+        <v>4.6945</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4786</v>
@@ -1477,7 +1477,7 @@
         <v>5.1728</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.7199</v>
+        <v>-4.719899999999999</v>
       </c>
       <c r="W13" t="n">
         <v>9.1249</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.046099999999999</v>
+        <v>9.0047</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2493</v>
+        <v>5.5431</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7968</v>
+        <v>3.4616</v>
       </c>
       <c r="G14" t="n">
         <v>3.1155</v>
@@ -1546,13 +1546,13 @@
         <v>3.7057</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2553</v>
+        <v>-1.2967</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2622</v>
+        <v>-0.9684</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9931</v>
+        <v>-0.3283</v>
       </c>
       <c r="V14" t="n">
         <v>4.4065</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7181</v>
+        <v>3.0617</v>
       </c>
       <c r="E15" t="n">
-        <v>2.449</v>
+        <v>2.6449</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2691</v>
+        <v>0.4168</v>
       </c>
       <c r="G15" t="n">
         <v>2.2449</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5268</v>
+        <v>-1.1832</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9849</v>
+        <v>-0.789</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5419</v>
+        <v>-0.3942</v>
       </c>
       <c r="V15" t="n">
         <v>1.2589</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2503</v>
+        <v>1.5172</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2173</v>
+        <v>1.801</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4676</v>
+        <v>-0.2838</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0177</v>
+        <v>1.6976</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8426</v>
+        <v>-0.8182</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8249</v>
+        <v>2.5158</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2034</v>
+        <v>2.437</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2449</v>
+        <v>1.1809</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0415</v>
+        <v>1.2561</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1857</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5977</v>
+        <v>-1.9991</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7834</v>
+        <v>1.2597</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3706</v>
+        <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.047</v>
+        <v>-0.2916</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3283</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2813</v>
+        <v>0.3793</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9444</v>
+        <v>-0.63</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3144</v>
+        <v>1.8877</v>
       </c>
       <c r="X16" t="n">
-        <v>0.63</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ANDRADE</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1242</v>
+        <v>1.0287</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.985</v>
+        <v>-0.2173</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1092</v>
+        <v>1.246</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7408</v>
+        <v>-0.0177</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7299</v>
+        <v>-0.8426</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0109</v>
+        <v>0.8249</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6102</v>
+        <v>-0.2034</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2228</v>
+        <v>-0.2449</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8329</v>
+        <v>0.0415</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1307</v>
+        <v>0.1857</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9527</v>
+        <v>-0.5977</v>
       </c>
       <c r="O17" t="n">
-        <v>0.822</v>
+        <v>0.7834</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.7057</v>
+        <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4034</v>
+        <v>-0.2686</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4452</v>
+        <v>-0.3283</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8486</v>
+        <v>0.0597</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4616</v>
+        <v>0.9444</v>
       </c>
       <c r="W17" t="n">
-        <v>3.776</v>
+        <v>0.3144</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>J. PINILLA NUÑEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0527</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2134</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6976</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8182</v>
+        <v>0.3221</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5158</v>
+        <v>0.6221</v>
       </c>
       <c r="J18" t="n">
-        <v>2.437</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1809</v>
+        <v>0.3221</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2561</v>
+        <v>0.6221</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9991</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2597</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.594</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7561</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2584</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5024</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PINILLA NUÑEZ</t>
+          <t>E. ANDRADE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.4851</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9441000000000001</v>
+        <v>-2.1809</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.666</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9441000000000001</v>
+        <v>-2.7408</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3221</v>
+        <v>-1.7299</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6221</v>
+        <v>-1.0109</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9441000000000001</v>
+        <v>-1.6102</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3221</v>
+        <v>0.2228</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6221</v>
+        <v>-1.8329</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.1307</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.9527</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.822</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.7057</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.2356</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.641</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.4054</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.4616</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.776</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.119</v>
+        <v>0.1442</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4315</v>
+        <v>-0.5294</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5505</v>
+        <v>0.6737</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8246</v>
@@ -2014,13 +2014,13 @@
         <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2798</v>
+        <v>-0.2546</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3867</v>
+        <v>-0.4846</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1069</v>
+        <v>0.23</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6294</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0596</v>
+        <v>-0.9349</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5576</v>
+        <v>-1.3026</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6172</v>
+        <v>0.3677</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2418</v>
+        <v>-1.5908</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4954</v>
+        <v>-0.7138</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2536</v>
+        <v>-0.8771</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.662</v>
+        <v>-1.1154</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7864</v>
+        <v>-0.5455</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1244</v>
+        <v>-0.5699</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5798</v>
+        <v>-0.4754</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.709</v>
+        <v>-0.1683</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1292</v>
+        <v>-0.3071</v>
       </c>
       <c r="P22" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2234</v>
+        <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>1.774</v>
+        <v>-0.4558</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5171</v>
+        <v>-0.1871</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2569</v>
+        <v>-0.2686</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8888</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>J. MALPICA PEREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2046</v>
+        <v>-1.3136</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4984</v>
+        <v>-0.0547</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2938</v>
+        <v>-1.2589</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5908</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7138</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8771</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1154</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5455</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5699</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4754</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1683</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3071</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7255</v>
+        <v>-0.0547</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.383</v>
+        <v>-0.0547</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3425</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MALPICA PEREZ</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3136</v>
+        <v>-1.9219</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0547</v>
+        <v>-1.0092</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2589</v>
+        <v>-0.9127</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-1.2418</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-2.4954</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1.2536</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.662</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-0.7864</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.1244</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>-0.5798</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>-1.709</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.1292</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.2234</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0547</v>
+        <v>-0.0883</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0547</v>
+        <v>-0.0497</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>-0.0386</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2589</v>
+        <v>-1.8888</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2589</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.2378</v>
+        <v>-2.5764</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7983</v>
+        <v>-3.2107</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5605</v>
+        <v>0.6343</v>
       </c>
       <c r="G25" t="n">
         <v>-3.3449</v>
@@ -2404,13 +2404,13 @@
         <v>3.1499</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1719</v>
+        <v>-0.5105</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.532</v>
+        <v>-0.9444</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3601</v>
+        <v>0.434</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9444</v>
@@ -2440,25 +2440,25 @@
         <v>9.3842</v>
       </c>
       <c r="E26" t="n">
-        <v>2.373499999999999</v>
+        <v>2.373599999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>7.010700000000001</v>
+        <v>7.010699999999998</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.7585</v>
+        <v>-1.758499999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.632099999999999</v>
+        <v>-8.632100000000001</v>
       </c>
       <c r="I26" t="n">
         <v>6.8735</v>
       </c>
       <c r="J26" t="n">
-        <v>2.966100000000001</v>
+        <v>2.9661</v>
       </c>
       <c r="K26" t="n">
-        <v>4.119900000000001</v>
+        <v>4.119899999999999</v>
       </c>
       <c r="L26" t="n">
         <v>-1.1536</v>
@@ -2470,7 +2470,7 @@
         <v>-12.752</v>
       </c>
       <c r="O26" t="n">
-        <v>8.027299999999999</v>
+        <v>8.0273</v>
       </c>
       <c r="P26" t="n">
         <v>11.1171</v>
@@ -2482,22 +2482,22 @@
         <v>20.3815</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.6944</v>
+        <v>-4.6943</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.173</v>
+        <v>-5.1728</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4786999999999999</v>
+        <v>0.4787000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>4.719900000000002</v>
+        <v>4.7199</v>
       </c>
       <c r="W26" t="n">
         <v>13.8446</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.124700000000001</v>
+        <v>-9.124699999999999</v>
       </c>
     </row>
   </sheetData>
